--- a/public/documents/pieces-reponse-2/R2-exposition-et-scenarios.xlsx
+++ b/public/documents/pieces-reponse-2/R2-exposition-et-scenarios.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposition" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scénarios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scénarios (fourchette)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,27 +58,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00DDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -87,7 +73,7 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -562,14 +548,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Rappel — initialement notifié</t>
+          <t>Rappel initial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total initial (proposition du 18/05/2026)</t>
+          <t>Total initial (18/05/2026)</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -579,18 +565,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dont amende 1759 (abandonnée après désignation)</t>
+          <t>dont amende 1759 (abandonnée)</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>471826</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Contrôle : 213 148 + 196 945 + 172 703 = 582 796 €</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -607,71 +586,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scénarios de réduction</t>
+          <t>Exposition résiduelle selon l'issue sur la reconstitution</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Scénario</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Effet</t>
+          <t>Société</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Associés</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1 — Reconstitution écartée (L. 52 / vice de méthode)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Plus de recette occultée : rappels société, distributions et taxation personnelle tombent. Exposition résiduelle ≈ 0 (hors accessoires éventuels).</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Annulation (L. 52 / vice de méthode)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2 — Reconstitution réduite</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Effet de levier ×4 du coefficient : chaque euro de boisson rendu à son usage réel retranche ~4 € au total, répercuté sur les distributions et l'impôt personnel.</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Réduction de 75 %</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>53287</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>92412</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>145699</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>3 — Reconstitution maintenue</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Leviers personnels : CSG/PS recalculées sans le 1,25 (QPC) ; décharge de la majoration 40 % faute de motivation individualisée ; contestation de la clé 50/50.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Réduction de 50 %</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>106574</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>184824</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>291398</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Maintien (hors réductions perso.)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>213148</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>369648</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>582796</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Effet de levier du coefficient : ~×4. Toute réduction du CA liquides se répercute sur société + associés.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
